--- a/assessment_forms/041_vascular_health_assessment_form--assessment_forms.xlsx
+++ b/assessment_forms/041_vascular_health_assessment_form--assessment_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -757,8 +757,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="21" customWidth="1" min="2" max="2"/>
+    <col width="21" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -820,12 +820,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_11,_'name':_'chest_pain',_'label':_'chest_pain',_'value':_'chest_pain'}</t>
+          <t>chest_pain</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 11, 'name': 'chest_pain', 'label': 'Chest Pain', 'value': 'Chest Pain'}</t>
+          <t>Chest Pain</t>
         </is>
       </c>
     </row>
@@ -837,12 +837,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_12,_'name':_'dizziness',_'label':_'dizziness',_'value':_'dizziness'}</t>
+          <t>dizziness</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 12, 'name': 'dizziness', 'label': 'Dizziness', 'value': 'Dizziness'}</t>
+          <t>Dizziness</t>
         </is>
       </c>
     </row>
@@ -854,12 +854,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_13,_'name':_'headache',_'label':_'headache',_'value':_'headache'}</t>
+          <t>headache</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 13, 'name': 'headache', 'label': 'Headache', 'value': 'Headache'}</t>
+          <t>Headache</t>
         </is>
       </c>
     </row>
@@ -871,12 +871,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_14,_'name':_'shortness_of_breath',_'label':_'shortness_of_breath',_'value':_'shortness_of_breath'}</t>
+          <t>shortness_of_breath</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 14, 'name': 'shortness_of_breath', 'label': 'Shortness of Breath', 'value': 'Shortness of Breath'}</t>
+          <t>Shortness of Breath</t>
         </is>
       </c>
     </row>
@@ -888,12 +888,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_15,_'name':_'chest_pain',_'label':_'chest_pain',_'value':_'chest_pain'}</t>
+          <t>chest_pain</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 15, 'name': 'chest_pain', 'label': 'Chest Pain', 'value': 'Chest Pain'}</t>
+          <t>Chest Pain</t>
         </is>
       </c>
     </row>
@@ -905,12 +905,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_16,_'name':_'dizziness',_'label':_'dizziness',_'value':_'dizziness'}</t>
+          <t>dizziness</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 16, 'name': 'dizziness', 'label': 'Dizziness', 'value': 'Dizziness'}</t>
+          <t>Dizziness</t>
         </is>
       </c>
     </row>
@@ -922,12 +922,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_17,_'name':_'headache',_'label':_'headache',_'value':_'headache'}</t>
+          <t>headache</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 17, 'name': 'headache', 'label': 'Headache', 'value': 'Headache'}</t>
+          <t>Headache</t>
         </is>
       </c>
     </row>
